--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -611,10 +611,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>31</v>
       </c>
       <c r="G6">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>9.6</v>
@@ -846,10 +846,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E6">
         <v>31</v>
@@ -1081,10 +1081,10 @@
         <v>15</v>
       </c>
       <c r="C6">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1093,7 +1093,7 @@
         <v>31</v>
       </c>
       <c r="G6">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H6">
         <v>9.6</v>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -94,22 +94,85 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ACEVEDO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MARIN</t>
   </si>
   <si>
-    <t>NUBE</t>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>ALEMAN</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
+    <t>TZOMPAXTLE</t>
+  </si>
+  <si>
+    <t>ALDAHIR</t>
+  </si>
+  <si>
+    <t>KAREN ITZEL</t>
+  </si>
+  <si>
+    <t>ZABDIEL</t>
   </si>
   <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
-    <t>CHRISTIAN YAIR</t>
+    <t>JORGE GUILLERMO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>GABRIELA DENISSE</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
   </si>
 </sst>
 </file>
@@ -507,7 +570,7 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -516,7 +579,7 @@
         <v>0</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2">
         <v>100</v>
@@ -663,7 +726,7 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -672,7 +735,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -754,19 +817,22 @@
         <v>11</v>
       </c>
       <c r="C2">
+        <v>38</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
         <v>37</v>
       </c>
-      <c r="D2">
-        <v>37</v>
-      </c>
-      <c r="E2">
-        <v>37</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.37</v>
+      </c>
+      <c r="H2">
+        <v>8.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -803,16 +869,19 @@
         <v>38</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>38</v>
       </c>
-      <c r="E4">
-        <v>38</v>
-      </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -826,16 +895,19 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>96</v>
+      </c>
+      <c r="H5">
+        <v>9.1</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -849,16 +921,19 @@
         <v>31</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>31</v>
       </c>
-      <c r="E6">
-        <v>31</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>9.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -872,16 +947,19 @@
         <v>27</v>
       </c>
       <c r="D7">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>74.06999999999999</v>
+      </c>
+      <c r="H7">
+        <v>7.9</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -892,19 +970,22 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>9.1</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -918,16 +999,19 @@
         <v>16</v>
       </c>
       <c r="D9">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>56.25</v>
+      </c>
+      <c r="H9">
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -977,22 +1061,22 @@
         <v>11</v>
       </c>
       <c r="C2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>37</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>97.37</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1044,7 +1128,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1070,7 +1154,7 @@
         <v>96</v>
       </c>
       <c r="H5">
-        <v>9.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1096,7 +1180,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1113,16 +1197,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F7">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G7">
-        <v>88.89</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H7">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1133,7 +1217,7 @@
         <v>17</v>
       </c>
       <c r="C8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -1142,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>100</v>
@@ -1165,16 +1249,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9">
-        <v>81.25</v>
+        <v>56.25</v>
       </c>
       <c r="H9">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -1184,7 +1268,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1216,22 +1300,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920126</v>
+        <v>21330051920001</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="D2" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1239,24 +1323,185 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920100</v>
+        <v>21330051920111</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920125</v>
+      </c>
+      <c r="B4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920126</v>
+      </c>
+      <c r="B5" t="s">
         <v>28</v>
       </c>
-      <c r="D3" t="s">
+      <c r="C5" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920190</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920213</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="C7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s">
         <v>16</v>
       </c>
-      <c r="G3">
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920123</v>
+      </c>
+      <c r="B8" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920132</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920201</v>
+      </c>
+      <c r="B10" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,12 @@
     <t>ACEVEDO</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -106,24 +112,33 @@
     <t>MARIN</t>
   </si>
   <si>
+    <t>LORENZO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>AGUILAR</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>OFICIAL</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
@@ -133,24 +148,33 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
+    <t>ROSALES</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>CORONADO</t>
+  </si>
+  <si>
+    <t>ARELLANO</t>
+  </si>
+  <si>
     <t>ROMERO</t>
   </si>
   <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
     <t>TZOMPAXTLE</t>
   </si>
   <si>
     <t>ALDAHIR</t>
   </si>
   <si>
+    <t>CANDIDO</t>
+  </si>
+  <si>
+    <t>AYLIN MELISSA</t>
+  </si>
+  <si>
     <t>KAREN ITZEL</t>
   </si>
   <si>
@@ -160,16 +184,22 @@
     <t>ALEJANDRO</t>
   </si>
   <si>
+    <t>GREGORIO</t>
+  </si>
+  <si>
+    <t>GUSTAVO</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>LIZBETH</t>
+  </si>
+  <si>
+    <t>GABRIELA DENISSE</t>
+  </si>
+  <si>
     <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
   </si>
   <si>
     <t>CLEMENTE</t>
@@ -846,16 +876,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="E3">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>76.67</v>
+      </c>
+      <c r="H3">
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1093,16 +1126,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>93.33</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1268,7 +1301,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1306,10 +1339,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1323,22 +1356,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920111</v>
+        <v>21330051920176</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1346,22 +1379,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920125</v>
+        <v>20330051920069</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1369,16 +1402,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920126</v>
+        <v>21330051920111</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -1392,22 +1425,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920190</v>
+        <v>21330051920125</v>
       </c>
       <c r="B6" t="s">
         <v>29</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1415,22 +1448,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920213</v>
+        <v>21330051920126</v>
       </c>
       <c r="B7" t="s">
         <v>30</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1438,7 +1471,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920123</v>
+        <v>21330051920386</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -1447,61 +1480,153 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920132</v>
+        <v>21330051920213</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920201</v>
+        <v>21330051920153</v>
       </c>
       <c r="B10" t="s">
         <v>33</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
       </c>
       <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920123</v>
+      </c>
+      <c r="B11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920132</v>
+      </c>
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920190</v>
+      </c>
+      <c r="B13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" t="s">
         <v>16</v>
       </c>
-      <c r="G10">
+      <c r="G13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920201</v>
+      </c>
+      <c r="B14" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="37">
   <si>
     <t>Mat</t>
   </si>
@@ -94,115 +94,40 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>ACEVEDO</t>
   </si>
   <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>MEZA</t>
   </si>
   <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ROSALES</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>CORONADO</t>
-  </si>
-  <si>
-    <t>ARELLANO</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>TZOMPAXTLE</t>
+    <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>ACSA FERNANDA</t>
   </si>
   <si>
     <t>ALDAHIR</t>
   </si>
   <si>
-    <t>CANDIDO</t>
-  </si>
-  <si>
     <t>AYLIN MELISSA</t>
-  </si>
-  <si>
-    <t>KAREN ITZEL</t>
-  </si>
-  <si>
-    <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>GUSTAVO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>LIZBETH</t>
-  </si>
-  <si>
-    <t>GABRIELA DENISSE</t>
-  </si>
-  <si>
-    <t>JORGE GUILLERMO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
   </si>
 </sst>
 </file>
@@ -876,19 +801,19 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F3">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G3">
-        <v>76.67</v>
+        <v>83.33</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1100,16 +1025,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>97.37</v>
+        <v>92.11</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1126,13 +1051,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>83.33</v>
+        <v>93.33</v>
       </c>
       <c r="H3">
         <v>7.3</v>
@@ -1161,7 +1086,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1178,16 +1103,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G5">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1213,7 +1138,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1230,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="G7">
-        <v>74.06999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="H7">
-        <v>7.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1282,13 +1207,13 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G9">
-        <v>56.25</v>
+        <v>81.25</v>
       </c>
       <c r="H9">
         <v>7.1</v>
@@ -1301,7 +1226,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1333,22 +1258,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920001</v>
+        <v>21330051920334</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1356,39 +1281,39 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920176</v>
+        <v>22330051920144</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920069</v>
+        <v>21330051920001</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
@@ -1397,236 +1322,29 @@
         <v>12</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920111</v>
+        <v>20330051920069</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920125</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920126</v>
-      </c>
-      <c r="B7" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" t="s">
-        <v>54</v>
-      </c>
-      <c r="E7" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" t="s">
-        <v>18</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920386</v>
-      </c>
-      <c r="B8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
-      </c>
-      <c r="E8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920213</v>
-      </c>
-      <c r="B9" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920153</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920123</v>
-      </c>
-      <c r="B11" t="s">
-        <v>34</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" t="s">
-        <v>58</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920132</v>
-      </c>
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E12" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920190</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E13" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920201</v>
-      </c>
-      <c r="B14" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="43">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,12 @@
     <t>BAEZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
@@ -109,6 +115,12 @@
     <t>ROMERO</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>MEZA</t>
   </si>
   <si>
@@ -119,6 +131,12 @@
   </si>
   <si>
     <t>JOSUE EDUARDO</t>
+  </si>
+  <si>
+    <t>JOSELIN</t>
+  </si>
+  <si>
+    <t>ALEJANDRO</t>
   </si>
   <si>
     <t>ACSA FERNANDA</t>
@@ -1103,16 +1121,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1190,7 +1208,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>9.1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1226,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1264,10 +1282,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
@@ -1281,70 +1299,116 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920144</v>
+        <v>21330051920149</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920001</v>
+        <v>21330051920126</v>
       </c>
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E4" t="s">
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920069</v>
+        <v>22330051920144</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920001</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920069</v>
+      </c>
+      <c r="B7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" t="s">
         <v>36</v>
       </c>
-      <c r="E5" t="s">
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
         <v>9</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F7" t="s">
         <v>12</v>
       </c>
-      <c r="G5">
+      <c r="G7">
         <v>1</v>
       </c>
     </row>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -1052,7 +1052,7 @@
         <v>92.11</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1078,7 +1078,7 @@
         <v>93.33</v>
       </c>
       <c r="H3">
-        <v>7.3</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1104,7 +1104,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1130,7 +1130,7 @@
         <v>88</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1156,7 +1156,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>9.5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1182,7 +1182,7 @@
         <v>96.3</v>
       </c>
       <c r="H7">
-        <v>7.5</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1208,7 +1208,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1234,7 +1234,7 @@
         <v>81.25</v>
       </c>
       <c r="H9">
-        <v>7.1</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
+++ b/docentes/García Sánchez Magda Bexabe - Estadisticos 20231.xlsx
@@ -1052,7 +1052,7 @@
         <v>92.11</v>
       </c>
       <c r="H2">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1078,7 +1078,7 @@
         <v>93.33</v>
       </c>
       <c r="H3">
-        <v>9.699999999999999</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1104,7 +1104,7 @@
         <v>100</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1130,7 +1130,7 @@
         <v>88</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1156,7 +1156,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1182,7 +1182,7 @@
         <v>96.3</v>
       </c>
       <c r="H7">
-        <v>9.800000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1208,7 +1208,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1234,7 +1234,7 @@
         <v>81.25</v>
       </c>
       <c r="H9">
-        <v>9.1</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
